--- a/LoanOfficer-A/2023/13 Haobijam Thasana.xlsx
+++ b/LoanOfficer-A/2023/13 Haobijam Thasana.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>17600</v>
+        <v>18400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6400</v>
+        <v>5600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -887,9 +887,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="1"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45379</v>
+      </c>
+      <c r="O3" s="4">
+        <v>200</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1">
       <c r="A4" s="1">
@@ -931,9 +937,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45380</v>
+      </c>
+      <c r="O4" s="4">
+        <v>200</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1">
       <c r="A5" s="1">
@@ -2107,9 +2119,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45374</v>
+      </c>
+      <c r="K31" s="4">
+        <v>200</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2145,9 +2163,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45378</v>
+      </c>
+      <c r="K32" s="4">
+        <v>200</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>
